--- a/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/JobSpecialization.xlsx
+++ b/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/JobSpecialization.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLab\REDIV\ReDiv_Online\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69986206-2EBF-423F-B395-9EA0C923BD95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C8C918-0551-4C5B-A2AF-E5A38494F880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="5910" windowWidth="44100" windowHeight="14560" xr2:uid="{7E696902-3033-486C-825F-94F8EB2A49C1}"/>
+    <workbookView xWindow="0" yWindow="5910" windowWidth="44100" windowHeight="14560" xr2:uid="{782E2B53-B118-4371-9A87-C8FEC1BA34F7}"/>
   </bookViews>
   <sheets>
     <sheet name="JobSpecialization" sheetId="2" r:id="rId1"/>
@@ -71,19 +71,19 @@
     <t>解锁等级(0=初始可用)</t>
   </si>
   <si>
-    <t>NameKey</t>
+    <t>Name</t>
   </si>
   <si>
     <t>string</t>
   </si>
   <si>
-    <t>专职名多语言Key(仅客户端)</t>
+    <t>专职名-中文原文(仅客户端)</t>
   </si>
   <si>
     <t>IconKey</t>
   </si>
   <si>
-    <t>专职卡图标Addressable Key(仅客户端)</t>
+    <t>专职卡图标Addressable完整路径(仅客户端)</t>
   </si>
   <si>
     <t>SortOrder</t>
@@ -92,13 +92,13 @@
     <t>界面排序(仅客户端)</t>
   </si>
   <si>
-    <t>Spec_Mage</t>
+    <t>魔法士</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Spec_Placeholder_02</t>
+    <t>占位专职</t>
   </si>
 </sst>
 </file>
@@ -482,7 +482,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B5BCE14-5324-4C4A-AB78-30C2CBE67DD5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6791D65E-96F9-4C64-90D2-2986EB6A2A75}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
